--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106425</v>
+        <v>106426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106426</v>
+        <v>106443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106459</v>
+        <v>106462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106462</v>
+        <v>106549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24720-2025 artfynd.xlsx
+++ b/artfynd/A 24720-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942054</v>
       </c>
       <c r="B2" t="n">
-        <v>106549</v>
+        <v>106812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
